--- a/Datos 05.05 - B.xlsx
+++ b/Datos 05.05 - B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="32">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -2374,6 +2374,65 @@
         <v>26</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>44110.86561420139</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
